--- a/dist/tally_templates/NSDC.xlsx
+++ b/dist/tally_templates/NSDC.xlsx
@@ -1204,7 +1204,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -2495,7 +2495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="474">
+  <cellXfs count="508">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3897,6 +3897,108 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3905,11 +4007,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4177,7 +4279,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y89"/>
   <sheetFormatPr defaultRowHeight="19.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -4978,14 +5080,14 @@
       <c r="D8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="185">
+      <c r="E8" s="200">
         <v>15</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="304" t="s">
+      <c r="H8" s="506" t="s">
         <v>105</v>
       </c>
       <c r="I8" s="304"/>
@@ -6173,14 +6275,14 @@
       <c r="D50" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="185">
+      <c r="E50" s="200">
         <v>15</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="H50" s="304" t="s">
+      <c r="H50" s="506" t="s">
         <v>105</v>
       </c>
       <c r="I50" s="304"/>
@@ -7360,7 +7462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
   </sheetPr>
@@ -8110,7 +8212,7 @@
       <c r="O6" s="198" t="s">
         <v>65</v>
       </c>
-      <c r="P6" s="199">
+      <c r="P6" s="491">
         <v>46208</v>
       </c>
       <c r="Q6" s="185"/>
@@ -8154,7 +8256,7 @@
       <c r="A8" s="198" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="198" t="s">
+      <c r="B8" s="200" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="198"/>
@@ -8174,7 +8276,7 @@
       <c r="O8" s="198" t="s">
         <v>78</v>
       </c>
-      <c r="P8" s="185">
+      <c r="P8" s="200">
         <v>15</v>
       </c>
       <c r="Q8" s="185"/>
@@ -8214,7 +8316,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="203" t="s">
         <v>11</v>
       </c>
@@ -8255,7 +8357,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="206"/>
       <c r="B11" s="206"/>
       <c r="C11" s="259"/>
@@ -9123,7 +9225,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
   </sheetPr>
@@ -9418,7 +9520,7 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" ht="24.3" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -9478,7 +9580,7 @@
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="474" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
@@ -9487,13 +9589,13 @@
       <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="475"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="476"/>
       <c r="L4" s="12"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
@@ -9540,20 +9642,20 @@
       <c r="A6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="15"/>
+      <c r="B6" s="475"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="475"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="17"/>
+      <c r="K6" s="477"/>
       <c r="L6" s="18" t="s">
         <v>9</v>
       </c>
@@ -10448,7 +10550,7 @@
       <c r="Y35" s="40"/>
     </row>
     <row r="36" ht="19.95" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="86"/>
+      <c r="A36" s="478"/>
       <c r="B36" s="63"/>
       <c r="C36" s="64" t="s">
         <v>18</v>
@@ -10477,7 +10579,7 @@
       <c r="Y36" s="40"/>
     </row>
     <row r="37" ht="19.95" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="86"/>
+      <c r="A37" s="478"/>
       <c r="B37" s="50"/>
       <c r="C37" s="51" t="s">
         <v>19</v>
@@ -10506,7 +10608,7 @@
       <c r="Y37" s="40"/>
     </row>
     <row r="38" ht="19.95" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="86"/>
+      <c r="A38" s="478"/>
       <c r="B38" s="57"/>
       <c r="C38" s="51" t="s">
         <v>18</v>
@@ -10535,7 +10637,7 @@
       <c r="Y38" s="40"/>
     </row>
     <row r="39" ht="19.95" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="86"/>
+      <c r="A39" s="478"/>
       <c r="B39" s="50"/>
       <c r="C39" s="51" t="s">
         <v>19</v>
@@ -10564,7 +10666,7 @@
       <c r="Y39" s="40"/>
     </row>
     <row r="40" ht="16.95" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="86"/>
+      <c r="A40" s="478"/>
       <c r="B40" s="57"/>
       <c r="C40" s="58" t="s">
         <v>18</v>
@@ -10593,7 +10695,7 @@
       <c r="Y40" s="40"/>
     </row>
     <row r="41" ht="16.95" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="86"/>
+      <c r="A41" s="478"/>
       <c r="B41" s="50"/>
       <c r="C41" s="58" t="s">
         <v>19</v>
@@ -10622,7 +10724,7 @@
       <c r="Y41" s="40"/>
     </row>
     <row r="42" ht="19.95" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="86"/>
+      <c r="A42" s="478"/>
       <c r="B42" s="61"/>
       <c r="C42" s="58" t="s">
         <v>18</v>
@@ -10651,7 +10753,7 @@
       <c r="Y42" s="40"/>
     </row>
     <row r="43" ht="19.95" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="86"/>
+      <c r="A43" s="478"/>
       <c r="B43" s="61"/>
       <c r="C43" s="58" t="s">
         <v>19</v>
@@ -10680,7 +10782,7 @@
       <c r="Y43" s="40"/>
     </row>
     <row r="44" ht="16.95" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="86"/>
+      <c r="A44" s="478"/>
       <c r="B44" s="63"/>
       <c r="C44" s="87" t="s">
         <v>18</v>
@@ -10709,7 +10811,7 @@
       <c r="Y44" s="40"/>
     </row>
     <row r="45" ht="16.95" customHeight="1" hidden="1" spans="1:25" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="90"/>
+      <c r="A45" s="479"/>
       <c r="B45" s="63"/>
       <c r="C45" s="62" t="s">
         <v>19</v>
@@ -12369,7 +12471,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
   </sheetPr>
@@ -13174,13 +13276,13 @@
       <c r="G6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="185"/>
+      <c r="H6" s="200"/>
       <c r="I6" s="185"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="199"/>
+      <c r="L6" s="491"/>
       <c r="M6" s="185"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -13226,7 +13328,7 @@
       <c r="A8" s="198" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="492" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="3"/>
@@ -13236,13 +13338,13 @@
       <c r="G8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="185"/>
+      <c r="H8" s="200"/>
       <c r="I8" s="185"/>
       <c r="J8" s="3"/>
       <c r="K8" s="198" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="185"/>
+      <c r="L8" s="200"/>
       <c r="M8" s="185"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -13284,7 +13386,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="201" t="s">
         <v>47</v>
       </c>
@@ -13329,7 +13431,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="204"/>
       <c r="B11" s="205"/>
       <c r="C11" s="205"/>
@@ -13359,19 +13461,19 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="18" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="207"/>
+      <c r="A12" s="493"/>
       <c r="B12" s="208"/>
       <c r="C12" s="209"/>
-      <c r="D12" s="210"/>
-      <c r="E12" s="211"/>
-      <c r="F12" s="212"/>
+      <c r="D12" s="494"/>
+      <c r="E12" s="495"/>
+      <c r="F12" s="496"/>
       <c r="G12" s="213"/>
       <c r="H12" s="214"/>
       <c r="I12" s="215"/>
       <c r="J12" s="216"/>
       <c r="K12" s="213"/>
       <c r="L12" s="213"/>
-      <c r="M12" s="217"/>
+      <c r="M12" s="50"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -13386,19 +13488,19 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="18" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="218"/>
+      <c r="A13" s="497"/>
       <c r="B13" s="202"/>
       <c r="C13" s="202"/>
-      <c r="D13" s="219"/>
-      <c r="E13" s="220"/>
-      <c r="F13" s="221"/>
+      <c r="D13" s="498"/>
+      <c r="E13" s="499"/>
+      <c r="F13" s="500"/>
       <c r="G13" s="202"/>
       <c r="H13" s="222"/>
       <c r="I13" s="223"/>
       <c r="J13" s="222"/>
       <c r="K13" s="202"/>
       <c r="L13" s="202"/>
-      <c r="M13" s="224"/>
+      <c r="M13" s="501"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -13413,19 +13515,19 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="207"/>
+      <c r="A14" s="493"/>
       <c r="B14" s="208"/>
       <c r="C14" s="209"/>
       <c r="D14" s="208"/>
-      <c r="E14" s="225"/>
-      <c r="F14" s="212"/>
+      <c r="E14" s="502"/>
+      <c r="F14" s="496"/>
       <c r="G14" s="213"/>
       <c r="H14" s="214"/>
       <c r="I14" s="215"/>
       <c r="J14" s="216"/>
       <c r="K14" s="213"/>
       <c r="L14" s="213"/>
-      <c r="M14" s="226"/>
+      <c r="M14" s="438"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -13440,19 +13542,19 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="207"/>
+      <c r="A15" s="493"/>
       <c r="B15" s="202"/>
       <c r="C15" s="202"/>
       <c r="D15" s="227"/>
-      <c r="E15" s="228"/>
-      <c r="F15" s="221"/>
+      <c r="E15" s="503"/>
+      <c r="F15" s="500"/>
       <c r="G15" s="202"/>
       <c r="H15" s="229"/>
       <c r="I15" s="230"/>
       <c r="J15" s="216"/>
       <c r="K15" s="213"/>
       <c r="L15" s="213"/>
-      <c r="M15" s="226"/>
+      <c r="M15" s="438"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -13467,19 +13569,19 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="218"/>
+      <c r="A16" s="497"/>
       <c r="B16" s="202"/>
       <c r="C16" s="202"/>
       <c r="D16" s="227"/>
-      <c r="E16" s="228"/>
-      <c r="F16" s="221"/>
+      <c r="E16" s="503"/>
+      <c r="F16" s="500"/>
       <c r="G16" s="202"/>
       <c r="H16" s="222"/>
       <c r="I16" s="223"/>
       <c r="J16" s="222"/>
       <c r="K16" s="202"/>
       <c r="L16" s="202"/>
-      <c r="M16" s="231"/>
+      <c r="M16" s="504"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -13494,19 +13596,19 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="218"/>
+      <c r="A17" s="497"/>
       <c r="B17" s="202"/>
       <c r="C17" s="202"/>
       <c r="D17" s="227"/>
-      <c r="E17" s="228"/>
-      <c r="F17" s="221"/>
+      <c r="E17" s="503"/>
+      <c r="F17" s="500"/>
       <c r="G17" s="202"/>
       <c r="H17" s="222"/>
       <c r="I17" s="223"/>
       <c r="J17" s="222"/>
       <c r="K17" s="202"/>
       <c r="L17" s="202"/>
-      <c r="M17" s="231"/>
+      <c r="M17" s="504"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -13521,19 +13623,19 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="218"/>
+      <c r="A18" s="497"/>
       <c r="B18" s="202"/>
       <c r="C18" s="202"/>
       <c r="D18" s="227"/>
-      <c r="E18" s="228"/>
-      <c r="F18" s="221"/>
+      <c r="E18" s="503"/>
+      <c r="F18" s="500"/>
       <c r="G18" s="202"/>
       <c r="H18" s="222"/>
       <c r="I18" s="223"/>
       <c r="J18" s="222"/>
       <c r="K18" s="202"/>
       <c r="L18" s="202"/>
-      <c r="M18" s="231"/>
+      <c r="M18" s="504"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -14243,7 +14345,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
   </sheetPr>
@@ -15038,7 +15140,7 @@
       <c r="A8" s="198" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="198" t="s">
+      <c r="B8" s="200" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="198"/>
@@ -15058,7 +15160,7 @@
       <c r="O8" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="P8" s="185">
+      <c r="P8" s="200">
         <v>15</v>
       </c>
       <c r="Q8" s="185"/>
@@ -15098,7 +15200,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="201" t="s">
         <v>11</v>
       </c>
@@ -15139,7 +15241,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="204"/>
       <c r="B11" s="204"/>
       <c r="C11" s="259"/>
@@ -16010,7 +16112,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y90"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="7" customHeight="1"/>
   <cols>
@@ -16113,7 +16215,7 @@
         <v>123</v>
       </c>
       <c r="B4" s="251"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="507" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="251"/>
@@ -16122,7 +16224,7 @@
       <c r="G4" s="251" t="s">
         <v>124</v>
       </c>
-      <c r="H4" s="251" t="s">
+      <c r="H4" s="507" t="s">
         <v>125</v>
       </c>
       <c r="I4" s="251"/>
@@ -16130,7 +16232,7 @@
       <c r="K4" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="L4" s="192" t="s">
+      <c r="L4" s="507" t="s">
         <v>32</v>
       </c>
       <c r="M4" s="40"/>
@@ -16926,7 +17028,7 @@
         <v>153</v>
       </c>
       <c r="G27" s="155"/>
-      <c r="H27" s="155" t="s">
+      <c r="H27" s="481" t="s">
         <v>154</v>
       </c>
       <c r="I27" s="155"/>
@@ -17916,7 +18018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -18619,21 +18721,21 @@
       <c r="A7" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="152" t="s">
+      <c r="B7" s="480" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="153"/>
       <c r="D7" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="120">
+      <c r="E7" s="480">
         <v>15</v>
       </c>
       <c r="F7" s="152"/>
       <c r="G7" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="155" t="s">
+      <c r="H7" s="481" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="9"/>
@@ -18771,7 +18873,7 @@
     <row r="12" ht="19.95" customHeight="1" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="160"/>
       <c r="B12" s="161"/>
-      <c r="C12" s="162"/>
+      <c r="C12" s="482"/>
       <c r="D12" s="162"/>
       <c r="E12" s="162"/>
       <c r="F12" s="162"/>
@@ -18798,7 +18900,7 @@
     <row r="13" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="163"/>
       <c r="B13" s="164"/>
-      <c r="C13" s="165"/>
+      <c r="C13" s="483"/>
       <c r="D13" s="165"/>
       <c r="E13" s="165"/>
       <c r="F13" s="165"/>
@@ -18825,7 +18927,7 @@
     <row r="14" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="163"/>
       <c r="B14" s="166"/>
-      <c r="C14" s="167"/>
+      <c r="C14" s="484"/>
       <c r="D14" s="168"/>
       <c r="E14" s="168"/>
       <c r="F14" s="168"/>
@@ -18854,7 +18956,7 @@
     <row r="15" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="163"/>
       <c r="B15" s="170"/>
-      <c r="C15" s="167"/>
+      <c r="C15" s="484"/>
       <c r="D15" s="168"/>
       <c r="E15" s="168"/>
       <c r="F15" s="168"/>
@@ -18881,7 +18983,7 @@
     <row r="16" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="171"/>
       <c r="B16" s="172"/>
-      <c r="C16" s="173"/>
+      <c r="C16" s="485"/>
       <c r="D16" s="174"/>
       <c r="E16" s="174"/>
       <c r="F16" s="174"/>
@@ -18908,7 +19010,7 @@
     <row r="17" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="176"/>
       <c r="B17" s="166"/>
-      <c r="C17" s="167"/>
+      <c r="C17" s="484"/>
       <c r="D17" s="168"/>
       <c r="E17" s="168"/>
       <c r="F17" s="168"/>
@@ -18935,7 +19037,7 @@
     <row r="18" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="177"/>
       <c r="B18" s="170"/>
-      <c r="C18" s="167"/>
+      <c r="C18" s="484"/>
       <c r="D18" s="168"/>
       <c r="E18" s="168"/>
       <c r="F18" s="168"/>
@@ -18962,7 +19064,7 @@
     <row r="19" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="163"/>
       <c r="B19" s="166"/>
-      <c r="C19" s="178"/>
+      <c r="C19" s="486"/>
       <c r="D19" s="179"/>
       <c r="E19" s="179"/>
       <c r="F19" s="179"/>
@@ -18989,7 +19091,7 @@
     <row r="20" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="181"/>
       <c r="B20" s="170"/>
-      <c r="C20" s="167"/>
+      <c r="C20" s="484"/>
       <c r="D20" s="168"/>
       <c r="E20" s="168"/>
       <c r="F20" s="168"/>
@@ -19016,7 +19118,7 @@
     <row r="21" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="182"/>
       <c r="B21" s="172"/>
-      <c r="C21" s="173"/>
+      <c r="C21" s="485"/>
       <c r="D21" s="174"/>
       <c r="E21" s="174"/>
       <c r="F21" s="174"/>
@@ -19043,7 +19145,7 @@
     <row r="22" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="183"/>
       <c r="B22" s="170"/>
-      <c r="C22" s="178"/>
+      <c r="C22" s="486"/>
       <c r="D22" s="179"/>
       <c r="E22" s="179"/>
       <c r="F22" s="179"/>
@@ -19070,7 +19172,7 @@
     <row r="23" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="184"/>
       <c r="B23" s="170"/>
-      <c r="C23" s="167"/>
+      <c r="C23" s="484"/>
       <c r="D23" s="168"/>
       <c r="E23" s="168"/>
       <c r="F23" s="168"/>
@@ -19097,7 +19199,7 @@
     <row r="24" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="163"/>
       <c r="B24" s="170"/>
-      <c r="C24" s="167"/>
+      <c r="C24" s="484"/>
       <c r="D24" s="168"/>
       <c r="E24" s="168"/>
       <c r="F24" s="168"/>
@@ -19124,7 +19226,7 @@
     <row r="25" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="186"/>
       <c r="B25" s="187"/>
-      <c r="C25" s="167"/>
+      <c r="C25" s="484"/>
       <c r="D25" s="168"/>
       <c r="E25" s="168"/>
       <c r="F25" s="168"/>
@@ -19151,7 +19253,7 @@
     <row r="26" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="171"/>
       <c r="B26" s="187"/>
-      <c r="C26" s="173"/>
+      <c r="C26" s="485"/>
       <c r="D26" s="174"/>
       <c r="E26" s="174"/>
       <c r="F26" s="174"/>
@@ -19178,7 +19280,7 @@
     <row r="27" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="29"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="178"/>
+      <c r="C27" s="486"/>
       <c r="D27" s="179"/>
       <c r="E27" s="179"/>
       <c r="F27" s="179"/>
@@ -19205,7 +19307,7 @@
     <row r="28" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="163"/>
       <c r="B28" s="187"/>
-      <c r="C28" s="188"/>
+      <c r="C28" s="487"/>
       <c r="D28" s="188"/>
       <c r="E28" s="188"/>
       <c r="F28" s="188"/>
@@ -19232,7 +19334,7 @@
     <row r="29" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="163"/>
       <c r="B29" s="166"/>
-      <c r="C29" s="188"/>
+      <c r="C29" s="487"/>
       <c r="D29" s="188"/>
       <c r="E29" s="188"/>
       <c r="F29" s="188"/>
@@ -19257,9 +19359,9 @@
       <c r="Y29" s="3"/>
     </row>
     <row r="30" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A30" s="189"/>
+      <c r="A30" s="488"/>
       <c r="B30" s="170"/>
-      <c r="C30" s="167"/>
+      <c r="C30" s="484"/>
       <c r="D30" s="168"/>
       <c r="E30" s="168"/>
       <c r="F30" s="168"/>
@@ -19284,9 +19386,9 @@
       <c r="Y30" s="3"/>
     </row>
     <row r="31" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A31" s="190"/>
+      <c r="A31" s="489"/>
       <c r="B31" s="172"/>
-      <c r="C31" s="173"/>
+      <c r="C31" s="485"/>
       <c r="D31" s="174"/>
       <c r="E31" s="174"/>
       <c r="F31" s="174"/>
@@ -19313,7 +19415,7 @@
     <row r="32" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="29"/>
       <c r="B32" s="166"/>
-      <c r="C32" s="178"/>
+      <c r="C32" s="486"/>
       <c r="D32" s="179"/>
       <c r="E32" s="179"/>
       <c r="F32" s="179"/>
@@ -19340,7 +19442,7 @@
     <row r="33" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="163"/>
       <c r="B33" s="187"/>
-      <c r="C33" s="188"/>
+      <c r="C33" s="487"/>
       <c r="D33" s="188"/>
       <c r="E33" s="188"/>
       <c r="F33" s="188"/>
@@ -19365,9 +19467,9 @@
       <c r="Y33" s="3"/>
     </row>
     <row r="34" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A34" s="189"/>
+      <c r="A34" s="488"/>
       <c r="B34" s="164"/>
-      <c r="C34" s="191"/>
+      <c r="C34" s="490"/>
       <c r="D34" s="191"/>
       <c r="E34" s="191"/>
       <c r="F34" s="191"/>
@@ -19392,9 +19494,9 @@
       <c r="Y34" s="3"/>
     </row>
     <row r="35" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A35" s="189"/>
+      <c r="A35" s="488"/>
       <c r="B35" s="166"/>
-      <c r="C35" s="188"/>
+      <c r="C35" s="487"/>
       <c r="D35" s="188"/>
       <c r="E35" s="188"/>
       <c r="F35" s="188"/>
@@ -19419,9 +19521,9 @@
       <c r="Y35" s="3"/>
     </row>
     <row r="36" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A36" s="190"/>
+      <c r="A36" s="489"/>
       <c r="B36" s="166"/>
-      <c r="C36" s="188"/>
+      <c r="C36" s="487"/>
       <c r="D36" s="188"/>
       <c r="E36" s="188"/>
       <c r="F36" s="188"/>
@@ -19718,7 +19820,7 @@
       <c r="Y46" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="36">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -19752,6 +19854,9 @@
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="G41:H41"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5511811023622047" right="0.3937007874015748" top="0.5511811023622047" bottom="0.31496062992125984" header="0.5118110236220472" footer="0.35433070866141736"/>
@@ -19760,7 +19865,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
   </sheetPr>
@@ -20564,13 +20669,13 @@
       <c r="G6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="185"/>
+      <c r="H6" s="200"/>
       <c r="I6" s="185"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="199"/>
+      <c r="L6" s="491"/>
       <c r="M6" s="185"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -20616,7 +20721,7 @@
       <c r="A8" s="198" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="492" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="274"/>
@@ -20626,13 +20731,13 @@
       <c r="G8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="185"/>
+      <c r="H8" s="200"/>
       <c r="I8" s="185"/>
       <c r="J8" s="3"/>
       <c r="K8" s="198" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="185"/>
+      <c r="L8" s="200"/>
       <c r="M8" s="185"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -20674,7 +20779,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="275" t="s">
         <v>47</v>
       </c>
@@ -20719,7 +20824,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="204"/>
       <c r="B11" s="35"/>
       <c r="C11" s="35"/>
@@ -20749,19 +20854,19 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="218"/>
+      <c r="A12" s="497"/>
       <c r="B12" s="202"/>
       <c r="C12" s="202"/>
       <c r="D12" s="227"/>
-      <c r="E12" s="228"/>
-      <c r="F12" s="221"/>
+      <c r="E12" s="503"/>
+      <c r="F12" s="500"/>
       <c r="G12" s="202"/>
       <c r="H12" s="222"/>
       <c r="I12" s="223"/>
       <c r="J12" s="222"/>
       <c r="K12" s="202"/>
       <c r="L12" s="202"/>
-      <c r="M12" s="277"/>
+      <c r="M12" s="270"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -20776,19 +20881,19 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="218"/>
+      <c r="A13" s="497"/>
       <c r="B13" s="202"/>
       <c r="C13" s="202"/>
       <c r="D13" s="227"/>
-      <c r="E13" s="228"/>
-      <c r="F13" s="221"/>
+      <c r="E13" s="503"/>
+      <c r="F13" s="500"/>
       <c r="G13" s="202"/>
       <c r="H13" s="222"/>
       <c r="I13" s="223"/>
       <c r="J13" s="222"/>
       <c r="K13" s="202"/>
       <c r="L13" s="202"/>
-      <c r="M13" s="277"/>
+      <c r="M13" s="270"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -20803,19 +20908,19 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="218"/>
+      <c r="A14" s="497"/>
       <c r="B14" s="202"/>
       <c r="C14" s="202"/>
       <c r="D14" s="227"/>
-      <c r="E14" s="228"/>
-      <c r="F14" s="221"/>
+      <c r="E14" s="503"/>
+      <c r="F14" s="500"/>
       <c r="G14" s="202"/>
       <c r="H14" s="222"/>
       <c r="I14" s="223"/>
       <c r="J14" s="222"/>
       <c r="K14" s="202"/>
       <c r="L14" s="202"/>
-      <c r="M14" s="277"/>
+      <c r="M14" s="270"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -20830,19 +20935,19 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="218"/>
+      <c r="A15" s="497"/>
       <c r="B15" s="202"/>
       <c r="C15" s="202"/>
       <c r="D15" s="227"/>
-      <c r="E15" s="228"/>
-      <c r="F15" s="221"/>
+      <c r="E15" s="503"/>
+      <c r="F15" s="500"/>
       <c r="G15" s="202"/>
       <c r="H15" s="222"/>
       <c r="I15" s="223"/>
       <c r="J15" s="222"/>
       <c r="K15" s="202"/>
       <c r="L15" s="202"/>
-      <c r="M15" s="277"/>
+      <c r="M15" s="270"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -20857,19 +20962,19 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="218"/>
+      <c r="A16" s="497"/>
       <c r="B16" s="202"/>
       <c r="C16" s="202"/>
       <c r="D16" s="227"/>
-      <c r="E16" s="228"/>
-      <c r="F16" s="221"/>
+      <c r="E16" s="503"/>
+      <c r="F16" s="500"/>
       <c r="G16" s="202"/>
       <c r="H16" s="222"/>
       <c r="I16" s="223"/>
       <c r="J16" s="222"/>
       <c r="K16" s="202"/>
       <c r="L16" s="202"/>
-      <c r="M16" s="277"/>
+      <c r="M16" s="270"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -20884,19 +20989,19 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="218"/>
+      <c r="A17" s="497"/>
       <c r="B17" s="202"/>
       <c r="C17" s="202"/>
       <c r="D17" s="227"/>
-      <c r="E17" s="228"/>
-      <c r="F17" s="221"/>
+      <c r="E17" s="503"/>
+      <c r="F17" s="500"/>
       <c r="G17" s="202"/>
       <c r="H17" s="222"/>
       <c r="I17" s="223"/>
       <c r="J17" s="222"/>
       <c r="K17" s="202"/>
       <c r="L17" s="202"/>
-      <c r="M17" s="277"/>
+      <c r="M17" s="270"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -20911,19 +21016,19 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" ht="19.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="218"/>
+      <c r="A18" s="497"/>
       <c r="B18" s="202"/>
       <c r="C18" s="202"/>
       <c r="D18" s="227"/>
-      <c r="E18" s="228"/>
-      <c r="F18" s="221"/>
+      <c r="E18" s="503"/>
+      <c r="F18" s="500"/>
       <c r="G18" s="202"/>
       <c r="H18" s="222"/>
       <c r="I18" s="223"/>
       <c r="J18" s="222"/>
       <c r="K18" s="202"/>
       <c r="L18" s="202"/>
-      <c r="M18" s="277"/>
+      <c r="M18" s="270"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -21546,7 +21651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y79"/>
   <sheetFormatPr defaultRowHeight="19.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -22223,7 +22328,7 @@
       <c r="F4" s="296" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="199"/>
+      <c r="G4" s="491"/>
       <c r="H4" s="185"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -22283,7 +22388,7 @@
       <c r="F6" s="296" t="s">
         <v>83</v>
       </c>
-      <c r="G6" s="295" t="s">
+      <c r="G6" s="505" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="3"/>
@@ -23347,7 +23452,7 @@
       <c r="F43" s="296" t="s">
         <v>83</v>
       </c>
-      <c r="G43" s="295" t="s">
+      <c r="G43" s="505" t="s">
         <v>26</v>
       </c>
       <c r="H43" s="3"/>
